--- a/安全告警_new.xlsx
+++ b/安全告警_new.xlsx
@@ -502,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -578,25 +578,125 @@
         <color indexed="8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
